--- a/src/main/java/testdata/TestDataExcel.xlsx
+++ b/src/main/java/testdata/TestDataExcel.xlsx
@@ -1,15 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28528"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28801"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D3CA7D56-D348-4B21-A523-8ECECAA67BD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E1BF89D-40C8-48A2-A5B8-263894844DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserConfig" sheetId="1" r:id="rId1"/>
     <sheet name="ZoneConfig" sheetId="2" r:id="rId2"/>
+    <sheet name="ShiftConfig" sheetId="3" r:id="rId3"/>
+    <sheet name="MachineConfig" sheetId="4" r:id="rId4"/>
+    <sheet name="LoggerConfig" sheetId="7" r:id="rId5"/>
+    <sheet name="TargetPartConfig" sheetId="8" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -32,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
   <si>
     <t>UserId</t>
   </si>
@@ -98,13 +102,242 @@
   </si>
   <si>
     <t>Zone-1</t>
+  </si>
+  <si>
+    <t>ShiftId</t>
+  </si>
+  <si>
+    <t>ShiftName</t>
+  </si>
+  <si>
+    <t>StartTime</t>
+  </si>
+  <si>
+    <t>EndTime</t>
+  </si>
+  <si>
+    <t>DowntimeDuration</t>
+  </si>
+  <si>
+    <t>DowntimeStart</t>
+  </si>
+  <si>
+    <t>Sh-1</t>
+  </si>
+  <si>
+    <t>Shift-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 04:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 00:30 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 07:00 </t>
+  </si>
+  <si>
+    <t>Sh-2</t>
+  </si>
+  <si>
+    <t>Shift-2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 20:00 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 14:00 </t>
+  </si>
+  <si>
+    <t>Sh-3</t>
+  </si>
+  <si>
+    <t>Shift-3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 22:00 </t>
+  </si>
+  <si>
+    <t>MachineId</t>
+  </si>
+  <si>
+    <t>MachineName</t>
+  </si>
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Manufacturer</t>
+  </si>
+  <si>
+    <t>Plant</t>
+  </si>
+  <si>
+    <t>Zone</t>
+  </si>
+  <si>
+    <t>MachineType</t>
+  </si>
+  <si>
+    <t>M1</t>
+  </si>
+  <si>
+    <t>Mach1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOGGER </t>
+  </si>
+  <si>
+    <t>Wimera</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Plant-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Zone-1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> CNC </t>
+  </si>
+  <si>
+    <t>M2</t>
+  </si>
+  <si>
+    <t>Mach2</t>
+  </si>
+  <si>
+    <t>M3</t>
+  </si>
+  <si>
+    <t>Mach3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> FOCAS </t>
+  </si>
+  <si>
+    <t>M4</t>
+  </si>
+  <si>
+    <t>Mach4</t>
+  </si>
+  <si>
+    <t>M5</t>
+  </si>
+  <si>
+    <t>Mach5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> REMON </t>
+  </si>
+  <si>
+    <t>LoggerType</t>
+  </si>
+  <si>
+    <t>LoggerId</t>
+  </si>
+  <si>
+    <t>LoggerName</t>
+  </si>
+  <si>
+    <t>IP</t>
+  </si>
+  <si>
+    <t>Port</t>
+  </si>
+  <si>
+    <t>Frequency</t>
+  </si>
+  <si>
+    <t>ConnectionTimeout</t>
+  </si>
+  <si>
+    <t>Machine</t>
+  </si>
+  <si>
+    <t>OEEType</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOGGER-4.0 </t>
+  </si>
+  <si>
+    <t>log1</t>
+  </si>
+  <si>
+    <t>logger1</t>
+  </si>
+  <si>
+    <t>121.121.121.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 10 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mach1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> With target Part </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LOGGER-5.0 </t>
+  </si>
+  <si>
+    <t>log2</t>
+  </si>
+  <si>
+    <t>logger2</t>
+  </si>
+  <si>
+    <t>121.121.121.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mach2</t>
+  </si>
+  <si>
+    <t>log3</t>
+  </si>
+  <si>
+    <t>logger3</t>
+  </si>
+  <si>
+    <t>121.121.121.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mach3</t>
+  </si>
+  <si>
+    <t>log4</t>
+  </si>
+  <si>
+    <t>logger4</t>
+  </si>
+  <si>
+    <t>121.121.121.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mach4</t>
+  </si>
+  <si>
+    <t>log5</t>
+  </si>
+  <si>
+    <t>logger5</t>
+  </si>
+  <si>
+    <t>121.121.121.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mach5</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,6 +358,14 @@
       <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -139,7 +380,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -162,12 +403,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -179,6 +435,14 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -629,4 +893,559 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B50C99-635E-481C-B4F0-CAE71D82A482}">
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="14.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="15.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9AC5EA-900C-4B9C-9C12-20700D72E744}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G2" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF17906-D6E7-458E-888D-2F79C075028E}">
+  <dimension ref="A1:K6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="11" max="11" width="20.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11">
+      <c r="A1" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="30.75">
+      <c r="A2" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" s="5">
+        <v>5854</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I2" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="K2" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="30.75">
+      <c r="A3" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="E3" s="5">
+        <v>5854</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I3" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J3" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="K3" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="30.75">
+      <c r="A4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="5">
+        <v>5854</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="30.75">
+      <c r="A5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="5">
+        <v>5854</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I5" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="30.75">
+      <c r="A6" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="5">
+        <v>5854</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="I6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AD5B65-9D6E-47EC-961E-974B2DAD98F7}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="8">
+        <v>100</v>
+      </c>
+      <c r="B2" s="8">
+        <v>100</v>
+      </c>
+      <c r="C2" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="8">
+        <v>100</v>
+      </c>
+      <c r="B3" s="8">
+        <v>100</v>
+      </c>
+      <c r="C3" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="8">
+        <v>100</v>
+      </c>
+      <c r="B4" s="8">
+        <v>100</v>
+      </c>
+      <c r="C4" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="8">
+        <v>100</v>
+      </c>
+      <c r="B5" s="8">
+        <v>100</v>
+      </c>
+      <c r="C5" s="8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="8">
+        <v>100</v>
+      </c>
+      <c r="B6" s="8">
+        <v>100</v>
+      </c>
+      <c r="C6" s="8">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/java/testdata/TestDataExcel.xlsx
+++ b/src/main/java/testdata/TestDataExcel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28801"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28803"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E1BF89D-40C8-48A2-A5B8-263894844DAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6FE0543-68F8-4ADD-860F-41EB4DC1FBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserConfig" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="100">
   <si>
     <t>UserId</t>
   </si>
@@ -150,15 +150,6 @@
   </si>
   <si>
     <t xml:space="preserve"> 14:00 </t>
-  </si>
-  <si>
-    <t>Sh-3</t>
-  </si>
-  <si>
-    <t>Shift-3</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 22:00 </t>
   </si>
   <si>
     <t>MachineId</t>
@@ -331,13 +322,28 @@
   </si>
   <si>
     <t xml:space="preserve"> Mach5</t>
+  </si>
+  <si>
+    <t>Shift1_Target</t>
+  </si>
+  <si>
+    <t>Shift2_Target</t>
+  </si>
+  <si>
+    <t>Machine1</t>
+  </si>
+  <si>
+    <t>Machine2</t>
+  </si>
+  <si>
+    <t>Machine3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -366,6 +372,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -380,7 +397,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -418,12 +435,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -442,7 +496,18 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -949,44 +1014,32 @@
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="13" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>40</v>
-      </c>
+      <c r="A4" s="12"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1006,140 +1059,140 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>44</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="E2" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="F2" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="G2" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="G3" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G4" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D5" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="G6" s="5" t="s">
         <v>51</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1156,217 +1209,218 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="14.5703125" customWidth="1"/>
     <col min="6" max="6" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="18.85546875" customWidth="1"/>
     <col min="11" max="11" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
       <c r="A1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="H1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>70</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="30.75">
       <c r="A2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="D2" s="5" t="s">
         <v>74</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>77</v>
       </c>
       <c r="E2" s="5">
         <v>5854</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30.75">
       <c r="A3" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>81</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="E3" s="5">
         <v>5854</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H3" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="30.75">
       <c r="A4" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E4" s="5">
         <v>5854</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30.75">
       <c r="A5" s="5" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E5" s="5">
         <v>5854</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="K5" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="30.75">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="E6" s="5">
         <v>5854</v>
       </c>
-      <c r="F6" s="7" t="s">
-        <v>78</v>
+      <c r="F6" s="8" t="s">
+        <v>75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
@@ -1376,74 +1430,70 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AD5B65-9D6E-47EC-961E-974B2DAD98F7}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="8">
+    <row r="1" spans="1:4">
+      <c r="A1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>95</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="D1" s="16"/>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="B2" s="11">
         <v>100</v>
       </c>
-      <c r="B2" s="8">
-        <v>100</v>
-      </c>
-      <c r="C2" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="8">
-        <v>100</v>
-      </c>
-      <c r="B3" s="8">
-        <v>100</v>
-      </c>
-      <c r="C3" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="8">
-        <v>100</v>
-      </c>
-      <c r="B4" s="8">
-        <v>100</v>
-      </c>
-      <c r="C4" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="8">
-        <v>100</v>
-      </c>
-      <c r="B5" s="8">
-        <v>100</v>
-      </c>
-      <c r="C5" s="8">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="8">
-        <v>100</v>
-      </c>
-      <c r="B6" s="8">
-        <v>100</v>
-      </c>
-      <c r="C6" s="8">
-        <v>100</v>
-      </c>
+      <c r="C2" s="15">
+        <v>110</v>
+      </c>
+      <c r="D2" s="17"/>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" s="11">
+        <v>150</v>
+      </c>
+      <c r="C3" s="15">
+        <v>160</v>
+      </c>
+      <c r="D3" s="17"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="11">
+        <v>120</v>
+      </c>
+      <c r="C4" s="15">
+        <v>130</v>
+      </c>
+      <c r="D4" s="17"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/java/testdata/TestDataExcel.xlsx
+++ b/src/main/java/testdata/TestDataExcel.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6FE0543-68F8-4ADD-860F-41EB4DC1FBBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:801_{9F5006E2-0EDD-42E8-8A41-8FA42B221BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="15525" windowHeight="11820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="UserConfig" sheetId="1" r:id="rId1"/>
@@ -15,21 +15,11 @@
     <sheet name="LoggerConfig" sheetId="7" r:id="rId5"/>
     <sheet name="TargetPartConfig" sheetId="8" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="0"/>
+  <oleSize ref="A1:L4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -343,7 +333,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -824,7 +814,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.42578125" customWidth="1"/>
     <col min="3" max="3" width="20" customWidth="1"/>
@@ -833,7 +823,7 @@
     <col min="6" max="6" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -853,7 +843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -873,7 +863,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -893,7 +883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="30.75">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -926,14 +916,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E40A600E-67DD-4472-9280-F9B9DD192D2B}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="12.7109375" customWidth="1"/>
     <col min="3" max="3" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
@@ -944,7 +934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>19</v>
       </c>
@@ -963,7 +953,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E7B50C99-635E-481C-B4F0-CAE71D82A482}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="14.140625" customWidth="1"/>
@@ -973,7 +963,7 @@
     <col min="6" max="6" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>22</v>
       </c>
@@ -993,7 +983,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>28</v>
       </c>
@@ -1013,7 +1003,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>34</v>
       </c>
@@ -1033,7 +1023,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="12"/>
       <c r="B4" s="12"/>
       <c r="C4" s="12"/>
@@ -1049,7 +1039,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9AC5EA-900C-4B9C-9C12-20700D72E744}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -1057,7 +1047,7 @@
     <col min="7" max="7" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>38</v>
       </c>
@@ -1080,7 +1070,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>45</v>
       </c>
@@ -1103,7 +1093,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>52</v>
       </c>
@@ -1126,7 +1116,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>54</v>
       </c>
@@ -1149,7 +1139,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>57</v>
       </c>
@@ -1172,7 +1162,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>59</v>
       </c>
@@ -1203,7 +1193,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EF17906-D6E7-458E-888D-2F79C075028E}">
   <dimension ref="A1:K6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
@@ -1213,7 +1203,7 @@
     <col min="11" max="11" width="20.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>62</v>
       </c>
@@ -1248,7 +1238,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="30.75">
+    <row r="2" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
         <v>71</v>
       </c>
@@ -1283,7 +1273,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30.75">
+    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>78</v>
       </c>
@@ -1318,7 +1308,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="30.75">
+    <row r="4" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>56</v>
       </c>
@@ -1353,7 +1343,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30.75">
+    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>56</v>
       </c>
@@ -1388,7 +1378,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="30.75">
+    <row r="6" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>61</v>
       </c>
@@ -1431,13 +1421,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3AD5B65-9D6E-47EC-961E-974B2DAD98F7}">
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
         <v>69</v>
       </c>
@@ -1449,7 +1439,7 @@
       </c>
       <c r="D1" s="16"/>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>97</v>
       </c>
@@ -1461,7 +1451,7 @@
       </c>
       <c r="D2" s="17"/>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" s="11" t="s">
         <v>98</v>
       </c>
@@ -1473,7 +1463,7 @@
       </c>
       <c r="D3" s="17"/>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
         <v>99</v>
       </c>
@@ -1485,12 +1475,12 @@
       </c>
       <c r="D4" s="17"/>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="9"/>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9"/>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
